--- a/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,160 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Candidate Filter Types</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KRDZA93Q75TMZP003XVTDN5E</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDZA93Q75TMZP003XVTDN5E</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Email Notification Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Email Notification Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,54 +781,76 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Email Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>

--- a/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,63 +583,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01KRDF11J7SF4BCNWJS86R9GXN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDF11J7SF4BCNWJS86R9GXN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Candidate Filter Types</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRDF11J7SF4BCNWJS86R9GXN</t>
+          <t>h_01KRDZA93Q75TMZP003XVTDN5E</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDF11J7SF4BCNWJS86R9GXN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDZA93Q75TMZP003XVTDN5E</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Candidate Filter Types</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KRDZA93Q75TMZP003XVTDN5E</t>
+          <t>h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDZA93Q75TMZP003XVTDN5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Email Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,98 +759,54 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Email Notification Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Attribute Map</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>

--- a/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,51 +617,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>General Settings:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KRDF11J7SF4BCNWJS86R9GXN</t>
+          <t>h_01KRK4TGDXNR7HMZJFPQY5BQNT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDF11J7SF4BCNWJS86R9GXN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK4TGDXNR7HMZJFPQY5BQNT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Candidate Filter Types</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRE0TH6TDSWF7H9FTYST9RZC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRDZA93Q75TMZP003XVTDN5E</t>
+          <t>h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRDZA93Q75TMZP003XVTDN5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,56 +715,56 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRFXQMPF423SM8VQW0CD7FRZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KRK6HBN9EJ6FAANP52RK84PB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK6HBN9EJ6FAANP52RK84PB</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Email Notification Settings</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KRK6HBN9RC1KTX4VRY5NNB2J</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK6HBN9RC1KTX4VRY5NNB2J</t>
         </is>
       </c>
     </row>
@@ -809,6 +809,50 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>General Settings:</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,107 +715,107 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KRK6HBN9EJ6FAANP52RK84PB</t>
+          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK6HBN9EJ6FAANP52RK84PB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KRK6HBN9RC1KTX4VRY5NNB2J</t>
+          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK6HBN9RC1KTX4VRY5NNB2J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Failure Notification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,32 +825,98 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KRK6HBN9EJ6FAANP52RK84PB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK6HBN9EJ6FAANP52RK84PB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KRK6HBN9RC1KTX4VRY5NNB2J</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01KRK6HBN9RC1KTX4VRY5NNB2J</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Zendesk-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
